--- a/app1/Excelfiles/July2023.xlsx
+++ b/app1/Excelfiles/July2023.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F285"/>
+  <dimension ref="A1:F286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.33203125" customWidth="1" style="2" min="1" max="1"/>
@@ -1895,13 +1895,18 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
       <c r="F285" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
